--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1dd__dd.leige.site\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{CD46D992-1759-47A1-BBB3-9466A3702517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFBC976-995E-423A-B5BB-22AC4A03872B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11508" yWindow="216" windowWidth="14244" windowHeight="15744"/>
+    <workbookView xWindow="1080" yWindow="360" windowWidth="14244" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>请按此提单</t>
     </r>
@@ -80,7 +79,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">件确认提单，并速发
 提单格式件给我司进行最终确认！
@@ -104,7 +102,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">操作
 </t>
@@ -130,7 +127,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">（通知人）
 </t>
@@ -214,7 +210,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>＆</t>
     </r>
@@ -249,7 +244,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">（收货人）
 AMAL ALFARSI CARGO SERVICES LLC  
@@ -266,7 +260,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -281,7 +274,7 @@
       <t xml:space="preserve">
 </t>
     </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -292,7 +285,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>发货人</t>
     </r>
@@ -311,21 +303,20 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>ZHEJIANG HUNTER SUPPLY CHAIN MANAGEMENT CO.,LTD
 (ADD:ROOM 1701-1710,BUILDING B,CHOUYIN MANSION,NO.188 SHANGCHENG ROAD,YIWU,CHINA (ZHEJIANG) PILOT FREE TRADE ZONE
 TEL:0579-85517798  FAX:0579-85517798
 E-MAIL:28962568@QQ.COM  地址电话传真邮箱只提供不显示)</t>
     </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>{提单号1}</t>
   </si>
   <si>
     <t>NINGBO</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>{船名}</t>
@@ -491,7 +482,6 @@
         <sz val="10"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>{无HS的商品列表1}</t>
     </r>
@@ -501,7 +491,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>{无HS的商品列表2}</t>
     </r>
@@ -522,7 +511,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>{无HS的商品列表4}</t>
     </r>
@@ -543,7 +531,6 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>{无HS的商品列表6}</t>
     </r>
@@ -558,14 +545,17 @@
       </rPr>
       <t>{无HS的商品列表7}</t>
     </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="26" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -583,26 +573,17 @@
       <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -615,7 +596,6 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -638,39 +618,27 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="24"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -709,7 +677,6 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -827,144 +794,148 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1308,7 +1279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1324,145 +1295,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="42" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="48" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:9" ht="36.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="45" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="45"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="27" t="s">
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
     </row>
     <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="40"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37" t="s">
+      <c r="B9" s="32"/>
+      <c r="C9" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="37"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="36" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="34" t="s">
         <v>33</v>
       </c>
@@ -1477,53 +1448,53 @@
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="35"/>
+      <c r="D12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="38"/>
+      <c r="E12" s="35"/>
       <c r="F12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="39"/>
+      <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="43" t="str">
         <f>C22&amp;"CTNS"</f>
         <v>0CTNS</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="49" t="s">
+      <c r="C13" s="44"/>
+      <c r="D13" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="46"/>
       <c r="F13" s="9" t="str">
         <f>E22&amp;"KGS"</f>
         <v>0KGS</v>
       </c>
-      <c r="G13" s="30" t="str">
+      <c r="G13" s="44" t="str">
         <f>G22&amp;"CBM"</f>
         <v>0CBM</v>
       </c>
-      <c r="H13" s="30"/>
+      <c r="H13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="33"/>
+      <c r="E14" s="48"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -1535,19 +1506,19 @@
       <c r="B15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="50" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="51" t="s">
         <v>37</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="51" t="s">
         <v>38</v>
       </c>
       <c r="H15" s="11" t="s">
@@ -1564,19 +1535,19 @@
       <c r="B16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="50" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="51" t="s">
         <v>43</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="51" t="s">
         <v>44</v>
       </c>
       <c r="H16" s="11" t="s">
@@ -1593,19 +1564,19 @@
       <c r="B17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="51" t="s">
         <v>50</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="51" t="s">
         <v>51</v>
       </c>
       <c r="H17" s="11" t="s">
@@ -1622,19 +1593,19 @@
       <c r="B18" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="50" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="51" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="51" t="s">
         <v>58</v>
       </c>
       <c r="H18" s="11" t="s">
@@ -1651,19 +1622,19 @@
       <c r="B19" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="50" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="51" t="s">
         <v>64</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="51" t="s">
         <v>65</v>
       </c>
       <c r="H19" s="11" t="s">
@@ -1680,19 +1651,19 @@
       <c r="B20" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="50" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="51" t="s">
         <v>71</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="51" t="s">
         <v>72</v>
       </c>
       <c r="H20" s="11" t="s">
@@ -1709,19 +1680,19 @@
       <c r="B21" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="50" t="s">
         <v>77</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="51" t="s">
         <v>78</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="51" t="s">
         <v>79</v>
       </c>
       <c r="H21" s="11" t="s">
@@ -1799,11 +1770,11 @@
       <c r="I26" s="18"/>
     </row>
     <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="19"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -1812,28 +1783,28 @@
       <c r="I27" s="18"/>
     </row>
     <row r="28" spans="1:9" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
       <c r="H28" s="21"/>
       <c r="I28" s="18"/>
     </row>
     <row r="29" spans="1:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
       <c r="H29" s="22"/>
       <c r="I29" s="18"/>
     </row>
@@ -1905,36 +1876,36 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:E11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A2:E5"/>
-    <mergeCell ref="F5:H9"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A2:E5"/>
+    <mergeCell ref="F5:H9"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.02" right="0.02" top="0.59" bottom="0.59" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1dd__dd.leige.site\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FED06F-9ADD-45F0-A658-A1E5F1DFA414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C33EB38-FFB0-4BB6-95C8-9404C3F37CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1032" yWindow="144" windowWidth="14244" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="14244" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,9 +145,6 @@
     <t>N/M</t>
   </si>
   <si>
-    <t>{无HS的商品列表1}{无HS的商品列表2}{无HS的商品列表3}{无HS的商品列表4}{无HS的商品列表5}{无HS的商品列表6}{无HS的商品列表7}</t>
-  </si>
-  <si>
     <t xml:space="preserve">申请14天免用箱 提单出SW
 </t>
   </si>
@@ -318,6 +315,86 @@
   </si>
   <si>
     <t>远通软件G3soft印制:www.g3soft.com      Tel:86-0574-87812201</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表1}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表2}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表3}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表4}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表5}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表6}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表7}</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -327,7 +404,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -439,6 +516,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -608,6 +693,59 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -615,11 +753,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -627,54 +760,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1033,15 +1118,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1052,71 +1137,71 @@
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
       <c r="E2" s="30"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="51" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
     </row>
     <row r="4" spans="1:9" ht="36.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="25" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="31" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
     </row>
     <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
@@ -1130,25 +1215,25 @@
       <c r="E8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="45" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="38"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
@@ -1160,22 +1245,22 @@
         <v>15</v>
       </c>
       <c r="E10" s="30"/>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
     </row>
     <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="44" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="38"/>
+      <c r="E11" s="28"/>
       <c r="F11" s="18" t="s">
         <v>19</v>
       </c>
@@ -1186,81 +1271,81 @@
       <c r="A12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="30"/>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="31" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="26"/>
     </row>
     <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="47" t="str">
+      <c r="B13" s="45" t="str">
         <f>SUM(C15:INDEX(C:C, MATCH(1E+99, C:C)-1)) &amp; "CTNS"</f>
         <v>0CTNS</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="28"/>
+        <v>82</v>
+      </c>
+      <c r="E13" s="26"/>
       <c r="F13" s="20" t="str">
         <f>SUM(E15:INDEX(E:E, MATCH(1E+99, E:E)-1)) &amp; "KGS"</f>
         <v>0KGS</v>
       </c>
-      <c r="G13" s="46" t="str">
+      <c r="G13" s="44" t="str">
         <f>SUM(G15:INDEX(G:G, MATCH(1E+99, G:G)-1)) &amp; "CBM"</f>
         <v>0CBM</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="26"/>
     </row>
     <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
-      <c r="D14" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="28"/>
+      <c r="D14" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="26"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="D15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="F15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="H15" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>3</v>
@@ -1268,176 +1353,176 @@
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="F16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="24" t="s">
+      <c r="H16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="D17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="F17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="24" t="s">
+      <c r="H17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="D18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="24" t="s">
+      <c r="F18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="24" t="s">
+      <c r="H18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="D19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="24" t="s">
+      <c r="F19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="24" t="s">
+      <c r="H19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="24" t="s">
+      <c r="F20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="24" t="s">
+      <c r="H20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="D21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="24" t="s">
+      <c r="F21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="24" t="s">
+      <c r="H21" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1494,24 +1579,24 @@
     </row>
     <row r="26" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="22"/>
+    </row>
+    <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="22"/>
-    </row>
-    <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="12"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
@@ -1519,42 +1604,32 @@
       <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:9" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
       <c r="H29" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A28:G28"/>
@@ -1571,7 +1646,17 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F5:H9"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.02" right="0.02" top="0.59" bottom="0.59" header="0" footer="0"/>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1dd__dd.leige.site\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C33EB38-FFB0-4BB6-95C8-9404C3F37CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6C3BBB-D3BF-48C1-A291-06BC7D54B387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="14244" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
   <si>
     <t>浙江猎人供应链管理有限公司
 提单OK件</t>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>B/L No.(提单号)</t>
-  </si>
-  <si>
-    <t>{提单号1}</t>
   </si>
   <si>
     <t xml:space="preserve">HT No. (业务编号)
@@ -191,9 +188,6 @@
     <t>CBM/{箱型2}</t>
   </si>
   <si>
-    <t>{提单号2}</t>
-  </si>
-  <si>
     <t>{箱号3}</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
     <t>CBM/{箱型3}</t>
   </si>
   <si>
-    <t>{提单号3}</t>
-  </si>
-  <si>
     <t>{箱号4}</t>
   </si>
   <si>
@@ -233,9 +224,6 @@
     <t>CBM/{箱型4}</t>
   </si>
   <si>
-    <t>{提单号4}</t>
-  </si>
-  <si>
     <t>{箱号5}</t>
   </si>
   <si>
@@ -254,9 +242,6 @@
     <t>CBM/{箱型5}</t>
   </si>
   <si>
-    <t>{提单号5}</t>
-  </si>
-  <si>
     <t>{箱号6}</t>
   </si>
   <si>
@@ -275,9 +260,6 @@
     <t>CBM/{箱型6}</t>
   </si>
   <si>
-    <t>{提单号6}</t>
-  </si>
-  <si>
     <t>{箱号7}</t>
   </si>
   <si>
@@ -294,9 +276,6 @@
   </si>
   <si>
     <t>CBM/{箱型7}</t>
-  </si>
-  <si>
-    <t>{提单号7}</t>
   </si>
   <si>
     <t>ON BOARD</t>
@@ -396,6 +375,33 @@
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>{并单号}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -404,7 +410,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -526,6 +532,12 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -693,36 +705,10 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -730,20 +716,35 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -756,10 +757,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1118,411 +1130,411 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="36" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="35" t="s">
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+    </row>
+    <row r="4" spans="1:9" ht="36.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-    </row>
-    <row r="4" spans="1:9" ht="36.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="46" t="s">
+      <c r="G4" s="44"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="49" t="s">
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+    </row>
+    <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-    </row>
-    <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+    </row>
+    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-    </row>
-    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="B8" s="34"/>
+      <c r="C8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="29" t="s">
+      <c r="D8" s="34"/>
+      <c r="E8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+    </row>
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="33" t="s">
+      <c r="D9" s="30"/>
+      <c r="E9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="18" t="s">
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="29" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="32" t="s">
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-    </row>
-    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="27" t="s">
+      <c r="E11" s="30"/>
+      <c r="F11" s="18" t="s">
         <v>18</v>
-      </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="18" t="s">
-        <v>19</v>
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="C12" s="34"/>
+      <c r="D12" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31" t="s">
+      <c r="E12" s="34"/>
+      <c r="F12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="19" t="s">
+      <c r="G12" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="26"/>
+      <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="45" t="str">
+        <v>24</v>
+      </c>
+      <c r="B13" s="41" t="str">
         <f>SUM(C15:INDEX(C:C, MATCH(1E+99, C:C)-1)) &amp; "CTNS"</f>
         <v>0CTNS</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="26"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="36"/>
       <c r="F13" s="20" t="str">
         <f>SUM(E15:INDEX(E:E, MATCH(1E+99, E:E)-1)) &amp; "KGS"</f>
         <v>0KGS</v>
       </c>
-      <c r="G13" s="44" t="str">
+      <c r="G13" s="40" t="str">
         <f>SUM(G15:INDEX(G:G, MATCH(1E+99, G:G)-1)) &amp; "CBM"</f>
         <v>0CBM</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
-      <c r="D14" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="26"/>
+      <c r="D14" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="36"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="D15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="F15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="H15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="I15" s="7" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="F16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="24" t="s">
+      <c r="H16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="F17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="H17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="I17" s="7" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="F18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="H18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="I18" s="7" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="I19" s="7" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="I20" s="7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1579,24 +1591,24 @@
     </row>
     <row r="26" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
+        <v>70</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
       <c r="H26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
+      <c r="A27" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
       <c r="D27" s="12"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
@@ -1604,59 +1616,59 @@
       <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:9" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
+      <c r="A28" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
+      <c r="A29" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F5:H9"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A2:E5"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A2:E5"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="C9:D9"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F5:H9"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="B26:G26"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.02" right="0.02" top="0.59" bottom="0.59" header="0" footer="0"/>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1dd__dd.leige.site\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6C3BBB-D3BF-48C1-A291-06BC7D54B387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABBEB39-66CD-4E9C-800B-853C32214BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="14244" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1335" yWindow="405" windowWidth="16920" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="84">
   <si>
     <t>浙江猎人供应链管理有限公司
 提单OK件</t>
@@ -376,7 +376,7 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{并单号}</t>
+    <t>{并单号1}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -385,15 +385,17 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>并单号</t>
-    </r>
-    <r>
-      <rPr>
+      <t>并单号1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -401,6 +403,144 @@
       <t>}</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号2}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号3}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号4}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号5}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号6}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并单号7}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
   </si>
 </sst>
 </file>
@@ -410,7 +550,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -535,6 +675,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -643,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -705,6 +852,55 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -713,64 +909,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1116,225 +1266,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="11" customWidth="1"/>
     <col min="4" max="4" width="12" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="11" customWidth="1"/>
     <col min="9" max="9" width="12" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="51" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="50" t="s">
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+    </row>
+    <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-    </row>
-    <row r="4" spans="1:9" ht="36.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="43" t="s">
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+    </row>
+    <row r="4" spans="1:9" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="44"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="46" t="s">
+    <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-    </row>
-    <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+    </row>
+    <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-    </row>
-    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+    </row>
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="39" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="30"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-    </row>
-    <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="42" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="48" t="s">
+      <c r="E10" s="30"/>
+      <c r="F10" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-    </row>
-    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="38" t="s">
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="34"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="28"/>
+    </row>
+    <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="41" t="str">
+      <c r="B13" s="43" t="str">
         <f>SUM(C15:INDEX(C:C, MATCH(1E+99, C:C)-1)) &amp; "CTNS"</f>
         <v>0CTNS</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37" t="s">
+      <c r="C13" s="28"/>
+      <c r="D13" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="20" t="str">
         <f>SUM(E15:INDEX(E:E, MATCH(1E+99, E:E)-1)) &amp; "KGS"</f>
         <v>0KGS</v>
       </c>
-      <c r="G13" s="40" t="str">
+      <c r="G13" s="50" t="str">
         <f>SUM(G15:INDEX(G:G, MATCH(1E+99, G:G)-1)) &amp; "CBM"</f>
         <v>0CBM</v>
       </c>
-      <c r="H13" s="36"/>
-    </row>
-    <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" s="28"/>
+    </row>
+    <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
@@ -1359,11 +1509,11 @@
       <c r="H15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="52" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -1388,11 +1538,11 @@
       <c r="H16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1417,11 +1567,11 @@
       <c r="H17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
@@ -1446,11 +1596,11 @@
       <c r="H18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="52" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>52</v>
       </c>
@@ -1475,11 +1625,11 @@
       <c r="H19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>58</v>
       </c>
@@ -1504,11 +1654,11 @@
       <c r="H20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>64</v>
       </c>
@@ -1533,11 +1683,11 @@
       <c r="H21" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5">
@@ -1557,7 +1707,7 @@
       <c r="H22" s="4"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="8"/>
@@ -1568,7 +1718,7 @@
       <c r="H23" s="21"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="8"/>
@@ -1579,7 +1729,7 @@
       <c r="H24" s="21"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="8"/>
@@ -1589,58 +1739,72 @@
       <c r="G25" s="9"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
       <c r="H26" s="22"/>
     </row>
-    <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+    <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="12"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
       <c r="H27" s="13"/>
     </row>
-    <row r="28" spans="1:9" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+    <row r="28" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
       <c r="H28" s="14"/>
     </row>
-    <row r="29" spans="1:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+    <row r="29" spans="1:9" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
       <c r="H29" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="D10:E10"/>
@@ -1655,20 +1819,6 @@
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="A2:E5"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="D14:E14"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.02" right="0.02" top="0.59" bottom="0.59" header="0" footer="0"/>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1dd__dd.leige.site\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABBEB39-66CD-4E9C-800B-853C32214BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D004442A-6858-4471-9EBC-32E23066653D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="405" windowWidth="16920" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="3315" windowWidth="16920" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>浙江猎人供应链管理有限公司
 提单OK件</t>
@@ -387,11 +387,31 @@
       <rPr>
         <b/>
         <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>单号</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>并单号1</t>
+      <t>1</t>
     </r>
     <r>
       <rPr>
@@ -404,144 +424,6 @@
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>并单号2}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>并单号3}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>并单号4}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>并单号5}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>并单号6}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>并单号7}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -550,7 +432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -568,16 +450,22 @@
       <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -600,11 +488,15 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="24"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -643,6 +535,8 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -686,6 +580,20 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -852,6 +760,9 @@
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -889,18 +800,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -909,6 +808,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -916,11 +818,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1280,149 +1188,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="38" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="37" t="s">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="25" t="s">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="31" t="s">
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="30"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="29" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="34" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="41" t="s">
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="18" t="s">
         <v>18</v>
       </c>
@@ -1433,53 +1341,53 @@
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="33" t="s">
+      <c r="C12" s="31"/>
+      <c r="D12" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="30"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="43" t="str">
+      <c r="B13" s="52" t="str">
         <f>SUM(C15:INDEX(C:C, MATCH(1E+99, C:C)-1)) &amp; "CTNS"</f>
         <v>0CTNS</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="40" t="s">
+      <c r="C13" s="29"/>
+      <c r="D13" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="28"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="20" t="str">
         <f>SUM(E15:INDEX(E:E, MATCH(1E+99, E:E)-1)) &amp; "KGS"</f>
         <v>0KGS</v>
       </c>
-      <c r="G13" s="50" t="str">
+      <c r="G13" s="48" t="str">
         <f>SUM(G15:INDEX(G:G, MATCH(1E+99, G:G)-1)) &amp; "CBM"</f>
         <v>0CBM</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
@@ -1509,7 +1417,7 @@
       <c r="H15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="52" t="s">
+      <c r="I15" s="25" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1523,14 +1431,16 @@
       <c r="C16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>29</v>
+      <c r="D16" s="4" t="str">
+        <f>IF(A16&lt;&gt;"","CTNS","")</f>
+        <v>CTNS</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>31</v>
+      <c r="F16" s="5" t="str">
+        <f>IF(A16&lt;&gt;"","KGS","")</f>
+        <v>KGS</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>38</v>
@@ -1538,8 +1448,9 @@
       <c r="H16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="52" t="s">
-        <v>78</v>
+      <c r="I16" s="25" t="str">
+        <f>IF(A16&lt;&gt;"",I15,"")</f>
+        <v>{并单号1}</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1552,14 +1463,16 @@
       <c r="C17" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>29</v>
+      <c r="D17" s="4" t="str">
+        <f>IF(A17&lt;&gt;"","CTNS","")</f>
+        <v>CTNS</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>31</v>
+      <c r="F17" s="5" t="str">
+        <f>IF(A17&lt;&gt;"","KGS","")</f>
+        <v>KGS</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>44</v>
@@ -1567,8 +1480,9 @@
       <c r="H17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="52" t="s">
-        <v>79</v>
+      <c r="I17" s="25" t="str">
+        <f>IF(A17&lt;&gt;"",I15,"")</f>
+        <v>{并单号1}</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1581,14 +1495,16 @@
       <c r="C18" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>29</v>
+      <c r="D18" s="4" t="str">
+        <f>IF(A18&lt;&gt;"","CTNS","")</f>
+        <v>CTNS</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>31</v>
+      <c r="F18" s="5" t="str">
+        <f>IF(A18&lt;&gt;"","KGS","")</f>
+        <v>KGS</v>
       </c>
       <c r="G18" s="24" t="s">
         <v>50</v>
@@ -1596,8 +1512,9 @@
       <c r="H18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="52" t="s">
-        <v>80</v>
+      <c r="I18" s="25" t="str">
+        <f>IF(A18&lt;&gt;"",I15,"")</f>
+        <v>{并单号1}</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1610,14 +1527,16 @@
       <c r="C19" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>29</v>
+      <c r="D19" s="4" t="str">
+        <f>IF(A19&lt;&gt;"","CTNS","")</f>
+        <v>CTNS</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>31</v>
+      <c r="F19" s="5" t="str">
+        <f>IF(A19&lt;&gt;"","KGS","")</f>
+        <v>KGS</v>
       </c>
       <c r="G19" s="24" t="s">
         <v>56</v>
@@ -1625,8 +1544,9 @@
       <c r="H19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="52" t="s">
-        <v>81</v>
+      <c r="I19" s="25" t="str">
+        <f>IF(A19&lt;&gt;"",I15,"")</f>
+        <v>{并单号1}</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1639,14 +1559,16 @@
       <c r="C20" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>29</v>
+      <c r="D20" s="4" t="str">
+        <f>IF(A20&lt;&gt;"","CTNS","")</f>
+        <v>CTNS</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>31</v>
+      <c r="F20" s="5" t="str">
+        <f>IF(A20&lt;&gt;"","KGS","")</f>
+        <v>KGS</v>
       </c>
       <c r="G20" s="24" t="s">
         <v>62</v>
@@ -1654,8 +1576,9 @@
       <c r="H20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="52" t="s">
-        <v>82</v>
+      <c r="I20" s="25" t="str">
+        <f>IF(A20&lt;&gt;"",I15,"")</f>
+        <v>{并单号1}</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1668,14 +1591,16 @@
       <c r="C21" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>29</v>
+      <c r="D21" s="4" t="str">
+        <f>IF(A21&lt;&gt;"","CTNS","")</f>
+        <v>CTNS</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>31</v>
+      <c r="F21" s="5" t="str">
+        <f>IF(A21&lt;&gt;"","KGS","")</f>
+        <v>KGS</v>
       </c>
       <c r="G21" s="24" t="s">
         <v>68</v>
@@ -1683,8 +1608,9 @@
       <c r="H21" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I21" s="52" t="s">
-        <v>83</v>
+      <c r="I21" s="25" t="str">
+        <f>IF(A21&lt;&gt;"",I15,"")</f>
+        <v>{并单号1}</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1743,22 +1669,22 @@
       <c r="A26" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
       <c r="H26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
       <c r="D27" s="12"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
@@ -1766,27 +1692,27 @@
       <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
       <c r="H29" s="15"/>
     </row>
   </sheetData>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1dd__dd.leige.site\projects\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D004442A-6858-4471-9EBC-32E23066653D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3B98B5-4B1E-4B5E-83FE-E9C95E2C54DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3315" windowWidth="16920" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11040" yWindow="135" windowWidth="16920" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1173,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="11" customWidth="1"/>
@@ -1185,9 +1185,10 @@
     <col min="7" max="7" width="11.7109375" style="11" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" style="11" customWidth="1"/>
     <col min="9" max="9" width="12" style="11" customWidth="1"/>
+    <col min="13" max="13" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1200,7 @@
       <c r="G1" s="29"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
@@ -1213,7 +1214,7 @@
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
     </row>
-    <row r="3" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="29"/>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -1225,7 +1226,7 @@
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
     </row>
-    <row r="4" spans="1:9" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="29"/>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
@@ -1237,7 +1238,7 @@
       <c r="G4" s="27"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="37"/>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -1249,7 +1250,7 @@
       <c r="G5" s="29"/>
       <c r="H5" s="29"/>
     </row>
-    <row r="6" spans="1:9" ht="105.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="105.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45" t="s">
         <v>5</v>
       </c>
@@ -1261,7 +1262,7 @@
       <c r="G6" s="29"/>
       <c r="H6" s="29"/>
     </row>
-    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45" t="s">
         <v>6</v>
       </c>
@@ -1273,7 +1274,7 @@
       <c r="G7" s="29"/>
       <c r="H7" s="29"/>
     </row>
-    <row r="8" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="30" t="s">
         <v>7</v>
       </c>
@@ -1289,7 +1290,7 @@
       <c r="G8" s="29"/>
       <c r="H8" s="29"/>
     </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="36" t="s">
         <v>10</v>
       </c>
@@ -1305,7 +1306,7 @@
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
     </row>
-    <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="30" t="s">
         <v>13</v>
       </c>
@@ -1321,7 +1322,7 @@
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
     </row>
-    <row r="11" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="36" t="s">
         <v>16</v>
       </c>
@@ -1337,7 +1338,7 @@
       <c r="G11" s="18"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
@@ -1357,7 +1358,7 @@
       </c>
       <c r="H12" s="29"/>
     </row>
-    <row r="13" spans="1:9" ht="343.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="343.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>24</v>
       </c>
@@ -1380,7 +1381,7 @@
       </c>
       <c r="H13" s="29"/>
     </row>
-    <row r="14" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -1392,7 +1393,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
@@ -1421,7 +1422,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -1432,28 +1433,32 @@
         <v>36</v>
       </c>
       <c r="D16" s="4" t="str">
-        <f>IF(A16&lt;&gt;"","CTNS","")</f>
+        <f t="shared" ref="D16:D21" si="0">IF(A16&lt;&gt;"","CTNS","")</f>
         <v>CTNS</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>37</v>
       </c>
       <c r="F16" s="5" t="str">
-        <f>IF(A16&lt;&gt;"","KGS","")</f>
+        <f t="shared" ref="F16:F21" si="1">IF(A16&lt;&gt;"","KGS","")</f>
         <v>KGS</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>39</v>
+      <c r="H16" s="4" t="str">
+        <f>IF(A16&lt;&gt;"",M16,"")</f>
+        <v>CBM/{箱型2}</v>
       </c>
       <c r="I16" s="25" t="str">
         <f>IF(A16&lt;&gt;"",I15,"")</f>
         <v>{并单号1}</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M16" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1464,28 +1469,32 @@
         <v>42</v>
       </c>
       <c r="D17" s="4" t="str">
-        <f>IF(A17&lt;&gt;"","CTNS","")</f>
+        <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>43</v>
       </c>
       <c r="F17" s="5" t="str">
-        <f>IF(A17&lt;&gt;"","KGS","")</f>
+        <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>45</v>
+      <c r="H17" s="4" t="str">
+        <f t="shared" ref="H17:H21" si="2">IF(A17&lt;&gt;"",M17,"")</f>
+        <v>CBM/{箱型3}</v>
       </c>
       <c r="I17" s="25" t="str">
         <f>IF(A17&lt;&gt;"",I15,"")</f>
         <v>{并单号1}</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
@@ -1496,28 +1505,32 @@
         <v>48</v>
       </c>
       <c r="D18" s="4" t="str">
-        <f>IF(A18&lt;&gt;"","CTNS","")</f>
+        <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>49</v>
       </c>
       <c r="F18" s="5" t="str">
-        <f>IF(A18&lt;&gt;"","KGS","")</f>
+        <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G18" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>51</v>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型4}</v>
       </c>
       <c r="I18" s="25" t="str">
         <f>IF(A18&lt;&gt;"",I15,"")</f>
         <v>{并单号1}</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>52</v>
       </c>
@@ -1528,28 +1541,32 @@
         <v>54</v>
       </c>
       <c r="D19" s="4" t="str">
-        <f>IF(A19&lt;&gt;"","CTNS","")</f>
+        <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="5" t="str">
-        <f>IF(A19&lt;&gt;"","KGS","")</f>
+        <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G19" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>57</v>
+      <c r="H19" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型5}</v>
       </c>
       <c r="I19" s="25" t="str">
         <f>IF(A19&lt;&gt;"",I15,"")</f>
         <v>{并单号1}</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>58</v>
       </c>
@@ -1560,28 +1577,32 @@
         <v>60</v>
       </c>
       <c r="D20" s="4" t="str">
-        <f>IF(A20&lt;&gt;"","CTNS","")</f>
+        <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>61</v>
       </c>
       <c r="F20" s="5" t="str">
-        <f>IF(A20&lt;&gt;"","KGS","")</f>
+        <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G20" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>63</v>
+      <c r="H20" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型6}</v>
       </c>
       <c r="I20" s="25" t="str">
         <f>IF(A20&lt;&gt;"",I15,"")</f>
         <v>{并单号1}</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M20" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>64</v>
       </c>
@@ -1592,28 +1613,32 @@
         <v>66</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f>IF(A21&lt;&gt;"","CTNS","")</f>
+        <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>67</v>
       </c>
       <c r="F21" s="5" t="str">
-        <f>IF(A21&lt;&gt;"","KGS","")</f>
+        <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G21" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>69</v>
+      <c r="H21" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型7}</v>
       </c>
       <c r="I21" s="25" t="str">
         <f>IF(A21&lt;&gt;"",I15,"")</f>
         <v>{并单号1}</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5">
@@ -1633,7 +1658,7 @@
       <c r="H22" s="4"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="8"/>
@@ -1644,7 +1669,7 @@
       <c r="H23" s="21"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="8"/>
@@ -1655,7 +1680,7 @@
       <c r="H24" s="21"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="8"/>
@@ -1665,7 +1690,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
         <v>70</v>
       </c>
@@ -1679,7 +1704,7 @@
       <c r="G26" s="37"/>
       <c r="H26" s="22"/>
     </row>
-    <row r="27" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41" t="s">
         <v>72</v>
       </c>
@@ -1691,7 +1716,7 @@
       <c r="G27" s="21"/>
       <c r="H27" s="13"/>
     </row>
-    <row r="28" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="46" t="s">
         <v>73</v>
       </c>
@@ -1703,7 +1728,7 @@
       <c r="G28" s="47"/>
       <c r="H28" s="14"/>
     </row>
-    <row r="29" spans="1:9" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
         <v>74</v>
       </c>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1\projects\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3B98B5-4B1E-4B5E-83FE-E9C95E2C54DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4ACDF0-F5BB-4C42-B0B1-E8D5202F6238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11040" yWindow="135" windowWidth="16920" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="150" windowWidth="13800" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>浙江猎人供应链管理有限公司
 提单OK件</t>
@@ -88,9 +88,6 @@
     <t>Voy.No.(航次)</t>
   </si>
   <si>
-    <t>Port pf Loading(装货港)</t>
-  </si>
-  <si>
     <t>{船名}</t>
   </si>
   <si>
@@ -281,19 +278,60 @@
     <t>ON BOARD</t>
   </si>
   <si>
-    <t xml:space="preserve">FREIGHT PREPAID
-SHIPPER LOAD,COUNT ＆ SEAL.
-CY-CY </t>
-  </si>
-  <si>
     <t>Total Number of Containers or Packages
 (In Words)集装箱或件数合计（大写）</t>
   </si>
   <si>
-    <t>No. of Original B(s)/L(正本提单份数)          打印人:  报表时间:2014-5-7 16:55:16</t>
-  </si>
-  <si>
     <t>远通软件G3soft印制:www.g3soft.com      Tel:86-0574-87812201</t>
+  </si>
+  <si>
+    <t>{并单号1}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>单号</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -376,51 +414,24 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{并单号1}</t>
+    <t>Port of Loading(装货港)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>{</t>
+      <t>FREIGHT PREPAID
+SHIPPER LOAD,COUNT &amp;</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
-      <t>并</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>单号</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
+      <t xml:space="preserve"> SEAL.
+CY-CY </t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1180,7 +1191,7 @@
     <col min="2" max="2" width="12.5703125" style="11" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" style="11" customWidth="1"/>
     <col min="4" max="4" width="12" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="11" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" style="11" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" style="11" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" style="11" customWidth="1"/>
@@ -1221,7 +1232,7 @@
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
       <c r="F3" s="38" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
@@ -1284,7 +1295,7 @@
       </c>
       <c r="D8" s="31"/>
       <c r="E8" s="17" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="F8" s="29"/>
       <c r="G8" s="29"/>
@@ -1292,15 +1303,15 @@
     </row>
     <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="37"/>
       <c r="C9" s="36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="37"/>
       <c r="E9" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="29"/>
       <c r="G9" s="29"/>
@@ -1308,59 +1319,59 @@
     </row>
     <row r="10" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31"/>
       <c r="D10" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="37"/>
       <c r="C11" s="37"/>
       <c r="D11" s="49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" s="37"/>
       <c r="F11" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>20</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="28" t="s">
         <v>22</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>23</v>
       </c>
       <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:13" ht="343.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="52" t="str">
         <f>SUM(C15:INDEX(C:C, MATCH(1E+99, C:C)-1)) &amp; "CTNS"</f>
@@ -1368,7 +1379,7 @@
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" s="29"/>
       <c r="F13" s="20" t="str">
@@ -1386,7 +1397,7 @@
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="21"/>
@@ -1395,56 +1406,56 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="D15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="F15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="H15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="I15" s="25" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="23" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>36</v>
       </c>
       <c r="D16" s="4" t="str">
         <f t="shared" ref="D16:D21" si="0">IF(A16&lt;&gt;"","CTNS","")</f>
         <v>CTNS</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" s="5" t="str">
         <f t="shared" ref="F16:F21" si="1">IF(A16&lt;&gt;"","KGS","")</f>
         <v>KGS</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H16" s="4" t="str">
         <f>IF(A16&lt;&gt;"",M16,"")</f>
@@ -1455,32 +1466,32 @@
         <v>{并单号1}</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>42</v>
       </c>
       <c r="D17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="5" t="str">
         <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17" s="4" t="str">
         <f t="shared" ref="H17:H21" si="2">IF(A17&lt;&gt;"",M17,"")</f>
@@ -1491,32 +1502,32 @@
         <v>{并单号1}</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="23" t="s">
         <v>47</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>48</v>
       </c>
       <c r="D18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18" s="5" t="str">
         <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H18" s="4" t="str">
         <f t="shared" si="2"/>
@@ -1527,32 +1538,32 @@
         <v>{并单号1}</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="23" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>54</v>
       </c>
       <c r="D19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" s="5" t="str">
         <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H19" s="4" t="str">
         <f t="shared" si="2"/>
@@ -1563,32 +1574,32 @@
         <v>{并单号1}</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="23" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>60</v>
       </c>
       <c r="D20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="5" t="str">
         <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H20" s="4" t="str">
         <f t="shared" si="2"/>
@@ -1599,32 +1610,32 @@
         <v>{并单号1}</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="23" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CTNS</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21" s="5" t="str">
         <f t="shared" si="1"/>
         <v>KGS</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H21" s="4" t="str">
         <f t="shared" si="2"/>
@@ -1635,7 +1646,7 @@
         <v>{并单号1}</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1692,10 +1703,10 @@
     </row>
     <row r="26" spans="1:13" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C26" s="37"/>
       <c r="D26" s="37"/>
@@ -1706,7 +1717,7 @@
     </row>
     <row r="27" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
@@ -1717,8 +1728,9 @@
       <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="46" t="s">
-        <v>73</v>
+      <c r="A28" s="46" t="str">
+        <f ca="1">"No. of Original B(s)/L(正本提单份数)      打印人:            报表时间:"&amp;TEXT(NOW(),"yyyy/m/d h:mm")</f>
+        <v>No. of Original B(s)/L(正本提单份数)      打印人:            报表时间:2026/4/17 9:52</v>
       </c>
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
@@ -1730,7 +1742,7 @@
     </row>
     <row r="29" spans="1:13" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B29" s="44"/>
       <c r="C29" s="44"/>

--- a/templates/总提单OK件的格式(无HS的.xlsx
+++ b/templates/总提单OK件的格式(无HS的.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd1\projects\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\1多文件批处理dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4ACDF0-F5BB-4C42-B0B1-E8D5202F6238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853C33E9-1CA7-4229-B4EF-D46A239F104D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="150" windowWidth="13800" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>浙江猎人供应链管理有限公司
 提单OK件</t>
@@ -330,6 +330,28 @@
         <family val="2"/>
       </rPr>
       <t>}</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Port of Loading(装货港)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>FREIGHT PREPAID
+SHIPPER LOAD,COUNT &amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> SEAL.
+CY-CY </t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -411,29 +433,149 @@
       </rPr>
       <t>{无HS的商品列表7}</t>
     </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Port of Loading(装货港)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <r>
-      <t>FREIGHT PREPAID
-SHIPPER LOAD,COUNT &amp;</t>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表8}</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> SEAL.
-CY-CY </t>
+      <t>{无HS的商品列表9}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表10}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表11}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{无HS的商品列表12}</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{箱号8}</t>
+  </si>
+  <si>
+    <t>{箱号9}</t>
+  </si>
+  <si>
+    <t>{箱号10}</t>
+  </si>
+  <si>
+    <t>{箱号11}</t>
+  </si>
+  <si>
+    <t>{箱号12}</t>
+  </si>
+  <si>
+    <t>{封号8}</t>
+  </si>
+  <si>
+    <t>{封号9}</t>
+  </si>
+  <si>
+    <t>{封号10}</t>
+  </si>
+  <si>
+    <t>{封号11}</t>
+  </si>
+  <si>
+    <t>{封号12}</t>
+  </si>
+  <si>
+    <t>{件数8}</t>
+  </si>
+  <si>
+    <t>{件数9}</t>
+  </si>
+  <si>
+    <t>{件数10}</t>
+  </si>
+  <si>
+    <t>{件数11}</t>
+  </si>
+  <si>
+    <t>{件数12}</t>
+  </si>
+  <si>
+    <t>{毛重8}</t>
+  </si>
+  <si>
+    <t>{毛重9}</t>
+  </si>
+  <si>
+    <t>{毛重10}</t>
+  </si>
+  <si>
+    <t>{毛重11}</t>
+  </si>
+  <si>
+    <t>{毛重12}</t>
+  </si>
+  <si>
+    <t>{体积8}</t>
+  </si>
+  <si>
+    <t>{体积9}</t>
+  </si>
+  <si>
+    <t>{体积10}</t>
+  </si>
+  <si>
+    <t>{体积11}</t>
+  </si>
+  <si>
+    <t>{体积12}</t>
+  </si>
+  <si>
+    <t>CBM/{箱型8}</t>
+  </si>
+  <si>
+    <t>CBM/{箱型9}</t>
+  </si>
+  <si>
+    <t>CBM/{箱型10}</t>
+  </si>
+  <si>
+    <t>CBM/{箱型11}</t>
+  </si>
+  <si>
+    <t>CBM/{箱型12}</t>
   </si>
 </sst>
 </file>
@@ -443,7 +585,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -605,6 +747,13 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -934,7 +1083,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1184,22 +1333,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="11" customWidth="1"/>
     <col min="4" max="4" width="12" style="11" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="11" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="11" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="11" customWidth="1"/>
     <col min="9" max="9" width="12" style="11" customWidth="1"/>
-    <col min="13" max="13" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -1211,7 +1360,7 @@
       <c r="G1" s="29"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
@@ -1225,7 +1374,7 @@
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
     </row>
-    <row r="3" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29"/>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -1237,7 +1386,7 @@
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
     </row>
-    <row r="4" spans="1:13" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="36.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
@@ -1249,7 +1398,7 @@
       <c r="G4" s="27"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -1261,7 +1410,7 @@
       <c r="G5" s="29"/>
       <c r="H5" s="29"/>
     </row>
-    <row r="6" spans="1:13" ht="105.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="105.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45" t="s">
         <v>5</v>
       </c>
@@ -1273,7 +1422,7 @@
       <c r="G6" s="29"/>
       <c r="H6" s="29"/>
     </row>
-    <row r="7" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>6</v>
       </c>
@@ -1285,7 +1434,7 @@
       <c r="G7" s="29"/>
       <c r="H7" s="29"/>
     </row>
-    <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>7</v>
       </c>
@@ -1295,13 +1444,13 @@
       </c>
       <c r="D8" s="31"/>
       <c r="E8" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="29"/>
       <c r="G8" s="29"/>
       <c r="H8" s="29"/>
     </row>
-    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
         <v>9</v>
       </c>
@@ -1317,7 +1466,7 @@
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
     </row>
-    <row r="10" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>12</v>
       </c>
@@ -1333,7 +1482,7 @@
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
     </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
         <v>15</v>
       </c>
@@ -1349,7 +1498,7 @@
       <c r="G11" s="18"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>18</v>
       </c>
@@ -1369,7 +1518,7 @@
       </c>
       <c r="H12" s="29"/>
     </row>
-    <row r="13" spans="1:13" ht="343.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>23</v>
       </c>
@@ -1379,7 +1528,7 @@
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="51" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" s="29"/>
       <c r="F13" s="20" t="str">
@@ -1392,7 +1541,7 @@
       </c>
       <c r="H13" s="29"/>
     </row>
-    <row r="14" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -1404,7 +1553,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1433,7 +1582,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
@@ -1444,14 +1593,14 @@
         <v>35</v>
       </c>
       <c r="D16" s="4" t="str">
-        <f t="shared" ref="D16:D21" si="0">IF(A16&lt;&gt;"","CTNS","")</f>
+        <f t="shared" ref="D16:D20" si="0">IF(A16&lt;&gt;"","CTNS","")</f>
         <v>CTNS</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="5" t="str">
-        <f t="shared" ref="F16:F21" si="1">IF(A16&lt;&gt;"","KGS","")</f>
+        <f t="shared" ref="F16:F20" si="1">IF(A16&lt;&gt;"","KGS","")</f>
         <v>KGS</v>
       </c>
       <c r="G16" s="24" t="s">
@@ -1469,7 +1618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>39</v>
       </c>
@@ -1494,7 +1643,7 @@
         <v>43</v>
       </c>
       <c r="H17" s="4" t="str">
-        <f t="shared" ref="H17:H21" si="2">IF(A17&lt;&gt;"",M17,"")</f>
+        <f t="shared" ref="H17:H26" si="2">IF(A17&lt;&gt;"",M17,"")</f>
         <v>CBM/{箱型3}</v>
       </c>
       <c r="I17" s="25" t="str">
@@ -1505,7 +1654,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -1541,7 +1690,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
@@ -1577,7 +1726,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
@@ -1613,7 +1762,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>63</v>
       </c>
@@ -1624,14 +1773,14 @@
         <v>65</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D21:D26" si="3">IF(A21&lt;&gt;"","CTNS","")</f>
         <v>CTNS</v>
       </c>
       <c r="E21" s="24" t="s">
         <v>66</v>
       </c>
       <c r="F21" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F21:F26" si="4">IF(A21&lt;&gt;"","KGS","")</f>
         <v>KGS</v>
       </c>
       <c r="G21" s="24" t="s">
@@ -1642,125 +1791,305 @@
         <v>CBM/{箱型7}</v>
       </c>
       <c r="I21" s="25" t="str">
-        <f>IF(A21&lt;&gt;"",I15,"")</f>
+        <f t="shared" ref="I21:I26" si="5">IF(A21&lt;&gt;"",I16,"")</f>
         <v>{并单号1}</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5">
+    <row r="22" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>CTNS</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>KGS</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型8}</v>
+      </c>
+      <c r="I22" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>{并单号1}</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>CTNS</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>KGS</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型9}</v>
+      </c>
+      <c r="I23" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>{并单号1}</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>CTNS</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>KGS</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型10}</v>
+      </c>
+      <c r="I24" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>{并单号1}</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>CTNS</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>KGS</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型11}</v>
+      </c>
+      <c r="I25" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>{并单号1}</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>CTNS</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>KGS</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>CBM/{箱型12}</v>
+      </c>
+      <c r="I26" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>{并单号1}</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="5">
         <f>SUM(C15:INDEX(C:C, ROW()-1))</f>
         <v>0</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="6">
+      <c r="D27" s="4"/>
+      <c r="E27" s="6">
         <f>SUM(E15:INDEX(E:E, ROW()-1))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6">
+      <c r="F27" s="5"/>
+      <c r="G27" s="6">
         <f>SUM(G15:INDEX(G:G, ROW()-1))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="21"/>
-    </row>
-    <row r="26" spans="1:13" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
+      <c r="H27" s="4"/>
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="1:13" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:13" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="22"/>
-    </row>
-    <row r="27" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="41" t="s">
+      <c r="B31" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" spans="1:13" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="46" t="str">
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="13"/>
+    </row>
+    <row r="33" spans="1:8" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="str">
         <f ca="1">"No. of Original B(s)/L(正本提单份数)      打印人:            报表时间:"&amp;TEXT(NOW(),"yyyy/m/d h:mm")</f>
-        <v>No. of Original B(s)/L(正本提单份数)      打印人:            报表时间:2026/4/17 9:52</v>
-      </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:13" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="43" t="s">
+        <v>No. of Original B(s)/L(正本提单份数)      打印人:            报表时间:2026/5/11 16:32</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" spans="1:8" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="15"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B31:G31"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D11:E11"/>
@@ -1787,7 +2116,7 @@
   <pageMargins left="0.02" right="0.02" top="0.59" bottom="0.59" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="29" max="16383" man="1"/>
+    <brk id="34" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>